--- a/artfynd/A 32606-2024 artfynd.xlsx
+++ b/artfynd/A 32606-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67468361</v>
+        <v>80162702</v>
       </c>
       <c r="B2" t="n">
-        <v>86136</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4379</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Toppvaxskivling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,19 +714,20 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Taljasjön Nallestugan 200 meter ovanför, Srm</t>
+          <t>Taljasjön, S om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592375.7148648208</v>
+        <v>592476</v>
       </c>
       <c r="R2" t="n">
-        <v>6548711.426222452</v>
+        <v>6548668</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,49 +772,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ove Unander</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ove Unander</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>78402690</v>
+        <v>80162774</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -836,13 +817,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -850,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592298.0129429157</v>
+        <v>592413</v>
       </c>
       <c r="R3" t="n">
-        <v>6548706.98044127</v>
+        <v>6548718</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,22 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-06-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-06-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,6 +874,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -915,58 +886,52 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Rolf Olsson, Björn Roesch</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79003804</v>
+        <v>80162812</v>
       </c>
       <c r="B4" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -974,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592505.8540406533</v>
+        <v>592485</v>
       </c>
       <c r="R4" t="n">
-        <v>6548656.957614895</v>
+        <v>6548688</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1004,27 +969,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På rotben av gammal rötskadad granlåga.Nordsluttning med gammal grandominerad skog med delvis inslag av tall och gammal asp. Död ved finns ojämnt spritt inom området. Delvis förekomst av mossbeklädda block.</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,22 +995,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79003899</v>
+        <v>79003804</v>
       </c>
       <c r="B5" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,38 +1013,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Taljasjön, Ö om, Srm</t>
+          <t>Taljasjön, S om, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592560.0417726401</v>
+        <v>592506</v>
       </c>
       <c r="R5" t="n">
-        <v>6548802.806616985</v>
+        <v>6548657</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1129,24 +1082,14 @@
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt på block.</t>
+          <t>På rotben av gammal rötskadad granlåga.Nordsluttning med gammal grandominerad skog med delvis inslag av tall och gammal asp. Död ved finns ojämnt spritt inom området. Delvis förekomst av mossbeklädda block.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,42 +1117,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79003792</v>
+        <v>87296761</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1217,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592505.8540406533</v>
+        <v>592517</v>
       </c>
       <c r="R6" t="n">
-        <v>6548656.957614895</v>
+        <v>6548643</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1247,27 +1194,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal granlåga. Nordsluttning med gammal grandominerad skog med delvis inslag av tall och gammal asp. Död ved finns ojämnt spritt inom området. Delvis förekomst av mossbeklädda block.</t>
+          <t>3 fräscha sporkapslar på kraftigt nedbruten rest av granlåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,22 +1225,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>79009165</v>
+        <v>95883672</v>
       </c>
       <c r="B7" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,50 +1243,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Taljasjön, S om, Srm</t>
+          <t>Taljasjön, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592134.0979763891</v>
+        <v>592588</v>
       </c>
       <c r="R7" t="n">
-        <v>6548644.907675757</v>
+        <v>6548847</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1381,22 +1300,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gammal asplåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,6 +1319,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1416,49 +1331,44 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>80162598</v>
+        <v>80162595</v>
       </c>
       <c r="B8" t="n">
-        <v>90661</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93207</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2058</v>
+        <v>789</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1474,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592497.8616193662</v>
+        <v>592498</v>
       </c>
       <c r="R8" t="n">
-        <v>6548689.170617439</v>
+        <v>6548689</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1507,19 +1417,14 @@
           <t>2019-09-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-09-27</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Vid viltstig.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1547,37 +1452,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80162742</v>
+        <v>79003792</v>
       </c>
       <c r="B9" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1590,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592510.9237765586</v>
+        <v>592506</v>
       </c>
       <c r="R9" t="n">
-        <v>6548639.076599324</v>
+        <v>6548657</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1620,27 +1520,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Allmänt förekommande.</t>
+          <t>På gammal granlåga. Nordsluttning med gammal grandominerad skog med delvis inslag av tall och gammal asp. Död ved finns ojämnt spritt inom området. Delvis förekomst av mossbeklädda block.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1661,44 +1551,39 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Karlsson, Bo Törnquist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>80162650</v>
+        <v>87296723</v>
       </c>
       <c r="B10" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1711,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592494.7906617853</v>
+        <v>592499</v>
       </c>
       <c r="R10" t="n">
-        <v>6548666.978015247</v>
+        <v>6548648</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1741,22 +1626,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Återfynd på granlåga.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1784,56 +1664,58 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>80162635</v>
+        <v>64491456</v>
       </c>
       <c r="B11" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>1445</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Taljasjön, S om, Srm</t>
+          <t>Skogen vid Taljasjön Brogetorp, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592496.0500183221</v>
+        <v>592414</v>
       </c>
       <c r="R11" t="n">
-        <v>6548678.839233772</v>
+        <v>6548691</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1857,22 +1739,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-03-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-03-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Där stigarna delar på sig ovanför Nallestugan..</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1888,53 +1765,56 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ove Unander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ove Unander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>80162748</v>
+        <v>80162598</v>
       </c>
       <c r="B12" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>2058</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1943,10 +1823,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592453.2059521934</v>
+        <v>592498</v>
       </c>
       <c r="R12" t="n">
-        <v>6548681.91950355</v>
+        <v>6548689</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1976,19 +1856,9 @@
           <t>2019-09-27</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,42 +1886,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>80162702</v>
+        <v>95883367</v>
       </c>
       <c r="B13" t="n">
-        <v>90642</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>150</v>
+        <v>2058</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2067,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592476.213460432</v>
+        <v>592478</v>
       </c>
       <c r="R13" t="n">
-        <v>6548668.072432645</v>
+        <v>6548678</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2097,22 +1962,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Nära viltstig. Närstående granar ej angripna av granbarkborrar. Däremot är angränsade granar angripna och dödade.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2140,61 +2000,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>80162812</v>
+        <v>79003899</v>
       </c>
       <c r="B14" t="n">
-        <v>90642</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>150</v>
+        <v>2671</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Taljasjön, S om, Srm</t>
+          <t>Taljasjön, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592485.0115625586</v>
+        <v>592560</v>
       </c>
       <c r="R14" t="n">
-        <v>6548687.831441859</v>
+        <v>6548803</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2221,22 +2069,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt på block.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2257,22 +2100,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Karlsson, Bo Törnquist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>80162746</v>
+        <v>80162646</v>
       </c>
       <c r="B15" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2280,21 +2118,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>4363</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2307,10 +2145,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592450.8916424015</v>
+        <v>592496</v>
       </c>
       <c r="R15" t="n">
-        <v>6548671.061607856</v>
+        <v>6548679</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2340,19 +2178,9 @@
           <t>2019-09-27</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2380,15 +2208,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>80162811</v>
+        <v>80162751</v>
       </c>
       <c r="B16" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,21 +2219,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>4363</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2423,10 +2246,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592473.1542420721</v>
+        <v>592453</v>
       </c>
       <c r="R16" t="n">
-        <v>6548688.059426697</v>
+        <v>6548682</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2456,24 +2279,9 @@
           <t>2019-09-27</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Allmänt förekommande.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2501,15 +2309,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>80162646</v>
+        <v>80162754</v>
       </c>
       <c r="B17" t="n">
-        <v>90649</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2544,10 +2347,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592496.0500183221</v>
+        <v>592419</v>
       </c>
       <c r="R17" t="n">
-        <v>6548678.839233772</v>
+        <v>6548685</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2577,19 +2380,9 @@
           <t>2019-09-27</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2617,37 +2410,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>80162719</v>
+        <v>80162635</v>
       </c>
       <c r="B18" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2660,10 +2448,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592472.8195420369</v>
+        <v>592496</v>
       </c>
       <c r="R18" t="n">
-        <v>6548659.245943179</v>
+        <v>6548679</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2693,24 +2481,9 @@
           <t>2019-09-27</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Allmänt förekommande.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2738,49 +2511,36 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>80162595</v>
+        <v>80162746</v>
       </c>
       <c r="B19" t="n">
-        <v>90663</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>789</v>
+        <v>4366</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2789,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592497.8616193662</v>
+        <v>592451</v>
       </c>
       <c r="R19" t="n">
-        <v>6548689.170617439</v>
+        <v>6548671</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2822,24 +2582,9 @@
           <t>2019-09-27</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Vid viltstig.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2867,37 +2612,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>80162751</v>
+        <v>80162748</v>
       </c>
       <c r="B20" t="n">
-        <v>90649</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4363</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2910,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592453.2059521934</v>
+        <v>592453</v>
       </c>
       <c r="R20" t="n">
-        <v>6548681.91950355</v>
+        <v>6548682</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2943,19 +2683,9 @@
           <t>2019-09-27</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2983,37 +2713,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>80163307</v>
+        <v>80162777</v>
       </c>
       <c r="B21" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3026,10 +2751,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>591682.7761678249</v>
+        <v>592424</v>
       </c>
       <c r="R21" t="n">
-        <v>6548856.794839797</v>
+        <v>6548719</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3056,22 +2781,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2019-09-28</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2019-09-28</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3092,48 +2807,51 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>80162570</v>
+        <v>87296694</v>
       </c>
       <c r="B22" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -3142,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592475.8971236403</v>
+        <v>592488</v>
       </c>
       <c r="R22" t="n">
-        <v>6548659.834656947</v>
+        <v>6548671</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3172,27 +2890,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Allmänt förekommande.</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3220,41 +2923,44 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>80162640</v>
+        <v>95883293</v>
       </c>
       <c r="B23" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3263,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592496.0500183221</v>
+        <v>592488</v>
       </c>
       <c r="R23" t="n">
-        <v>6548678.839233772</v>
+        <v>6548676</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3293,27 +2999,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-02</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Allmänt förekommande.</t>
+          <t>På gränsen mellan levande och barkborredödade granar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3341,15 +3037,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>80162738</v>
+        <v>67468361</v>
       </c>
       <c r="B24" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89085</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3357,40 +3048,47 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>4379</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Taljasjön, S om, Srm</t>
+          <t>Taljasjön Nallestugan 200 meter ovanför, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592490.8817847576</v>
+        <v>592376</v>
       </c>
       <c r="R24" t="n">
-        <v>6548658.139064921</v>
+        <v>6548711</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3414,27 +3112,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Allmänt förekommande.</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3450,49 +3133,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ove Unander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ove Unander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>87296723</v>
+        <v>80162650</v>
       </c>
       <c r="B25" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3505,10 +3183,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592498.8551706013</v>
+        <v>592495</v>
       </c>
       <c r="R25" t="n">
-        <v>6548648.043979204</v>
+        <v>6548667</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3535,27 +3213,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Återfynd på granlåga.</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3583,51 +3246,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>87296761</v>
+        <v>80162570</v>
       </c>
       <c r="B26" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>210</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3635,10 +3284,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592517.0168524627</v>
+        <v>592476</v>
       </c>
       <c r="R26" t="n">
-        <v>6548642.82452909</v>
+        <v>6548660</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3665,27 +3314,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>3 fräscha sporkapslar på kraftigt nedbruten rest av granlåga.</t>
+          <t>Allmänt förekommande.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3713,49 +3352,36 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>87296694</v>
+        <v>80162640</v>
       </c>
       <c r="B27" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3764,10 +3390,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592487.9963351947</v>
+        <v>592496</v>
       </c>
       <c r="R27" t="n">
-        <v>6548670.928951225</v>
+        <v>6548679</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3794,22 +3420,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Allmänt förekommande.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3837,19 +3458,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>87296628</v>
+        <v>80162719</v>
       </c>
       <c r="B28" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3862,24 +3478,16 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3888,10 +3496,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592478.9930308497</v>
+        <v>592473</v>
       </c>
       <c r="R28" t="n">
-        <v>6548680.999118994</v>
+        <v>6548659</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3918,22 +3526,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Allmänt förekommande.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3961,49 +3564,36 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>95883293</v>
+        <v>80162738</v>
       </c>
       <c r="B29" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -4012,10 +3602,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592488.3871526481</v>
+        <v>592491</v>
       </c>
       <c r="R29" t="n">
-        <v>6548676.082214479</v>
+        <v>6548658</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4042,27 +3632,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gränsen mellan levande och barkborredödade granar.</t>
+          <t>Allmänt förekommande.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4090,19 +3670,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>95883092</v>
+        <v>80162742</v>
       </c>
       <c r="B30" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -4115,12 +3690,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4133,10 +3708,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592469.8904488256</v>
+        <v>592511</v>
       </c>
       <c r="R30" t="n">
-        <v>6548695.181917308</v>
+        <v>6548639</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4163,27 +3738,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Närstående granar ej angripna av granbarkborrar. Däremot är angränsadegranar angripna och dödade.</t>
+          <t>Allmänt förekommande.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4211,19 +3776,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>95883659</v>
+        <v>80162783</v>
       </c>
       <c r="B31" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -4236,12 +3796,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4254,10 +3814,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592516.0412298843</v>
+        <v>592424</v>
       </c>
       <c r="R31" t="n">
-        <v>6548704.526851534</v>
+        <v>6548719</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4284,22 +3844,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Allmänt förekommande.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4327,19 +3882,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>95883336</v>
+        <v>80162811</v>
       </c>
       <c r="B32" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4352,12 +3902,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4370,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592470.1635922646</v>
+        <v>592473</v>
       </c>
       <c r="R32" t="n">
-        <v>6548683.872154091</v>
+        <v>6548688</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4400,27 +3950,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Närstående granar ej angripna av granbarkborrar. Däremot är angränsade granar angripna och dödade.</t>
+          <t>Allmänt förekommande.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4448,15 +3988,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>95883672</v>
+        <v>80163307</v>
       </c>
       <c r="B33" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4464,21 +3999,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>366</v>
+        <v>5964</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4487,14 +4022,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Taljasjön, Ö om, Srm</t>
+          <t>Taljasjön, S om, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592588.3389599439</v>
+        <v>591683</v>
       </c>
       <c r="R33" t="n">
-        <v>6548847.211656529</v>
+        <v>6548857</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4521,27 +4056,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gammal asplåga.</t>
+          <t>2019-09-28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4562,26 +4082,21 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>95883718</v>
+        <v>87296628</v>
       </c>
       <c r="B34" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4594,16 +4109,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -4612,10 +4135,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592501.6413129888</v>
+        <v>592479</v>
       </c>
       <c r="R34" t="n">
-        <v>6548639.366720563</v>
+        <v>6548681</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4642,27 +4165,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>I anslutning till ännu ej barkborreangripna granar.</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4690,19 +4198,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>95883124</v>
+        <v>95883092</v>
       </c>
       <c r="B35" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4715,12 +4218,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4733,10 +4236,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>592451.9461610671</v>
+        <v>592470</v>
       </c>
       <c r="R35" t="n">
-        <v>6548712.751813049</v>
+        <v>6548695</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4766,24 +4269,14 @@
           <t>2021-09-02</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2021-09-02</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Närstående granar ej angripna av granbarkborrar. Däremot är angränsade granar angripna och dödade.</t>
+          <t>Närstående granar ej angripna av granbarkborrar. Däremot är angränsadegranar angripna och dödade.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4811,19 +4304,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>95883169</v>
+        <v>95883124</v>
       </c>
       <c r="B36" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4836,12 +4324,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4854,10 +4342,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>592455.6564469512</v>
+        <v>592452</v>
       </c>
       <c r="R36" t="n">
-        <v>6548729.815801632</v>
+        <v>6548713</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4887,19 +4375,14 @@
           <t>2021-09-02</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2021-09-02</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Närstående granar ej angripna av granbarkborrar. Däremot är angränsade granar angripna och dödade.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4927,19 +4410,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>95883709</v>
+        <v>95883169</v>
       </c>
       <c r="B37" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4952,12 +4430,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4970,10 +4448,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>592501.3308184006</v>
+        <v>592455</v>
       </c>
       <c r="R37" t="n">
-        <v>6548652.21887141</v>
+        <v>6548730</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5003,24 +4481,9 @@
           <t>2021-09-02</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2021-09-02</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>I anslutning till ännu ej barkborreangripna granar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5048,49 +4511,36 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>95883367</v>
+        <v>95883336</v>
       </c>
       <c r="B38" t="n">
-        <v>90661</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2058</v>
+        <v>5964</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
@@ -5099,10 +4549,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592478.0251207016</v>
+        <v>592470</v>
       </c>
       <c r="R38" t="n">
-        <v>6548678.403833939</v>
+        <v>6548684</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5132,24 +4582,14 @@
           <t>2021-09-02</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2021-09-02</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Nära viltstig. Närstående granar ej angripna av granbarkborrar. Däremot är angränsade granar angripna och dödade.</t>
+          <t>Närstående granar ej angripna av granbarkborrar. Däremot är angränsade granar angripna och dödade.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5174,6 +4614,646 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>95883659</v>
+      </c>
+      <c r="B39" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Taljasjön, S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>592516</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6548705</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>95883709</v>
+      </c>
+      <c r="B40" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Taljasjön, S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>592502</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6548653</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>I anslutning till ännu ej barkborreangripna granar.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>95883718</v>
+      </c>
+      <c r="B41" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Taljasjön, S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>592502</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6548640</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>I anslutning till ännu ej barkborreangripna granar.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>79009165</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Taljasjön, S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>592134</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6548645</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>87296804</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Taljasjön, S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>592429</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6548652</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2020-08-05</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2020-08-05</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>82405163</v>
+      </c>
+      <c r="B44" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Taljasjön, S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>592184</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6548647</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2020-02-24</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2020-02-24</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Enstak blåsippor i blom.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32606-2024 artfynd.xlsx
+++ b/artfynd/A 32606-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80162702</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80162774</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80162812</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79003804</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1229,6 +1254,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87296761</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1335,6 +1365,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95883672</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80162595</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1555,6 +1595,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79003792</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1661,6 +1706,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87296723</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1774,6 +1824,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64491456</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1883,6 +1938,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80162598</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1997,6 +2057,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95883367</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2104,6 +2169,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79003899</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2205,6 +2275,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80162646</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2306,6 +2381,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80162751</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2407,6 +2487,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80162754</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2508,6 +2593,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80162635</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2609,6 +2699,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80162746</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2710,6 +2805,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80162748</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2811,6 +2911,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80162777</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2920,6 +3025,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87296694</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3034,6 +3144,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95883293</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3142,6 +3257,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67468361</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3243,6 +3363,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80162650</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3349,6 +3474,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80162570</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3455,6 +3585,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80162640</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3561,6 +3696,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80162719</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3667,6 +3807,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80162738</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3773,6 +3918,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80162742</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3879,6 +4029,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80162783</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3985,6 +4140,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80162811</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4086,6 +4246,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80163307</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4195,6 +4360,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87296628</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4301,6 +4471,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95883092</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4407,6 +4582,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95883124</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4508,6 +4688,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95883169</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4614,6 +4799,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95883336</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4715,6 +4905,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95883659</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4821,6 +5016,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95883709</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4927,6 +5127,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95883718</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5040,6 +5245,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79009165</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5147,6 +5357,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87296804</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5254,8 +5469,58 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82405163</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>